--- a/shuttle-web/public/전년도_자료_입력_시트_양식.xlsx
+++ b/shuttle-web/public/전년도_자료_입력_시트_양식.xlsx
@@ -8,114 +8,66 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\OneDrive\바탕 화면\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6D6BF0-986E-4FA0-904A-B0E43AC7022C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B231F99-DD1F-405D-AB73-8565207B1774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="초-중-고등부" sheetId="1" r:id="rId1"/>
-    <sheet name="유치원부" sheetId="2" r:id="rId2"/>
+    <sheet name="유치원부" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>반명</t>
+  </si>
+  <si>
+    <t>학생이름/영문이름</t>
+  </si>
+  <si>
+    <t>연령</t>
+  </si>
+  <si>
+    <t>성별</t>
+  </si>
   <si>
     <t>보호자 성함</t>
   </si>
   <si>
-    <t>반명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>학교명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>학년</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연라</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>주소</t>
+  </si>
+  <si>
+    <t>담임명</t>
+  </si>
+  <si>
+    <t>등원시간</t>
+  </si>
+  <si>
+    <t>하원시간</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>유치원명</t>
   </si>
   <si>
     <t>부모연락처</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>성별</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>학생이름/영문이름</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유치원명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>하원정보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>정규하원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>방과후하원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>종일반하원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>비고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>담임명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보호자연락처</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>등원차량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>하원차량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연령</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>등원시간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>하원시간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>등원지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>하원지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -138,27 +90,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -166,76 +106,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -575,198 +456,96 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q24"/>
-  <sheetFormatPr defaultRowHeight="27" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="22.77734375" customWidth="1"/>
-    <col min="13" max="16" width="10.77734375" customWidth="1"/>
-    <col min="17" max="17" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:15" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q2" s="2"/>
-    </row>
-    <row r="24" spans="12:12" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L24" t="s">
-        <v>4</v>
-      </c>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{338CD320-D1FA-4FC1-8CBA-47E9C765EA3C}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="21.77734375" customWidth="1"/>
-    <col min="11" max="11" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="I1:I2"/>
+  <mergeCells count="13">
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="J1:L1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -775,13 +554,12 @@
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="I1:I2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:O2" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>